--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,48 +786,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128519867</v>
+        <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spelbacken Stenträsket, Nb</t>
+          <t>Spelbacken, Gråträsk, V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>722331</v>
+        <v>722360</v>
       </c>
       <c r="R3" t="n">
-        <v>7265026</v>
+        <v>7264840</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,6 +872,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,16 +890,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128519867</t>
+          <t>https://artportalen.se/Sighting/136735616</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128519868</v>
+        <v>128519867</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>722422</v>
+        <v>722331</v>
       </c>
       <c r="R4" t="n">
-        <v>7264541</v>
+        <v>7265026</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -984,38 +992,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128519868</t>
+          <t>https://artportalen.se/Sighting/128519867</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128519859</v>
+        <v>128519868</v>
       </c>
       <c r="B5" t="n">
-        <v>80493</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>722478</v>
+        <v>722422</v>
       </c>
       <c r="R5" t="n">
-        <v>7264884</v>
+        <v>7264541</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,54 +1094,54 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128519859</t>
+          <t>https://artportalen.se/Sighting/128519868</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128519861</v>
+        <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>80461</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spelbacken Stenträsket, Nb</t>
+          <t>Spelbacken, Gråträsk, V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>722451</v>
+        <v>722146</v>
       </c>
       <c r="R6" t="n">
-        <v>7264857</v>
+        <v>7265129</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1165,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,54 +1206,57 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128519861</t>
+          <t>https://artportalen.se/Sighting/136735611</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128519862</v>
+        <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>80461</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spelbacken Stenträsket, Nb</t>
+          <t>Spelbacken, Gråträsk, V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>722391</v>
+        <v>722384</v>
       </c>
       <c r="R7" t="n">
-        <v>7265002</v>
+        <v>7264848</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1259,12 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1273,6 +1294,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1290,54 +1312,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128519862</t>
+          <t>https://artportalen.se/Sighting/136735615</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128519863</v>
+        <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>80461</v>
+        <v>78877</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spelbacken Stenträsket, Nb</t>
+          <t>Spelbacken, Gråträsk, V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>722406</v>
+        <v>722356</v>
       </c>
       <c r="R8" t="n">
-        <v>7265010</v>
+        <v>7264995</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1383,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,54 +1424,57 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128519863</t>
+          <t>https://artportalen.se/Sighting/136735613</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128519864</v>
+        <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>80461</v>
+        <v>78877</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spelbacken Stenträsket, Nb</t>
+          <t>Spelbacken, Gråträsk, V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>722448</v>
+        <v>722390</v>
       </c>
       <c r="R9" t="n">
-        <v>7264951</v>
+        <v>7264691</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1463,12 +1498,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1477,6 +1512,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1494,16 +1530,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128519864</t>
+          <t>https://artportalen.se/Sighting/136735618</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128519866</v>
+        <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>58057</v>
+        <v>80093</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,49 +1547,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spelbacken Stenträsket, Nb</t>
+          <t>Spelbacken, Gråträsk, V Piteå, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>722316</v>
+        <v>722364</v>
       </c>
       <c r="R10" t="n">
-        <v>7265018</v>
+        <v>7264819</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,27 +1604,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 3 stycken</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,6 +1618,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1623,16 +1636,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128519866</t>
+          <t>https://artportalen.se/Sighting/136735617</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128519865</v>
+        <v>128519859</v>
       </c>
       <c r="B11" t="n">
-        <v>97983</v>
+        <v>80493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1640,21 +1653,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>722267</v>
+        <v>722478</v>
       </c>
       <c r="R11" t="n">
-        <v>7265006</v>
+        <v>7264884</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1725,7 +1738,882 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/128519859</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128519861</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Spelbacken Stenträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>722451</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7264857</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519861</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128519862</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Spelbacken Stenträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>722391</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7265002</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519862</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128519863</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spelbacken Stenträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>722406</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7265010</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519863</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128519864</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Spelbacken Stenträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>722448</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7264951</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519864</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136735614</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Spelbacken, Gråträsk, V Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>722384</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7264932</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735614</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128519866</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Spelbacken Stenträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>722316</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7265018</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst 3 stycken</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128519866</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128519865</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Spelbacken Stenträsket, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>722267</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7265006</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128519865</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136735612</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98208</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Spelbacken, Gråträsk, V Piteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>722306</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7265029</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735612</t>
         </is>
       </c>
     </row>
@@ -1741,6 +2629,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136735614</v>
       </c>
       <c r="B16" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136735614</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136735614</v>
       </c>
       <c r="B16" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -816,11 +816,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -2187,11 +2183,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -2502,7 +2502,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136735616</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>136735611</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>136735615</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>136735613</v>
       </c>
       <c r="B8" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136735618</v>
       </c>
       <c r="B9" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>136735617</v>
       </c>
       <c r="B10" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136735614</v>
       </c>
       <c r="B16" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 41283-2025 artfynd.xlsx
+++ b/artfynd/A 41283-2025 artfynd.xlsx
@@ -2502,7 +2502,7 @@
         <v>136735612</v>
       </c>
       <c r="B19" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
